--- a/backtest_runs/20260410_193731/by_symbol/MACFL/MACFL.xlsx
+++ b/backtest_runs/20260410_193731/by_symbol/MACFL/MACFL.xlsx
@@ -465,12 +465,12 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>same_side_as_oracle</t>
+          <t>same_side_as_actual</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>daily_pnl_diff_oracle_minus_model</t>
+          <t>daily_pnl_diff_actual_minus_model</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
@@ -480,7 +480,7 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>suggestion_oracle</t>
+          <t>suggestion_actual</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
@@ -490,7 +490,7 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>daily_pnl_oracle</t>
+          <t>daily_pnl_actual</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
@@ -500,7 +500,7 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>equity_oracle</t>
+          <t>equity_actual</t>
         </is>
       </c>
     </row>
@@ -541,7 +541,7 @@
         <v>-277.9200000000105</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K2" s="2" t="n">
         <v>99722.07999999999</v>
@@ -633,7 +633,7 @@
         <v>-2640.240000000001</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K4" s="2" t="n">
         <v>101991.76</v>
@@ -679,7 +679,7 @@
         <v>-10097.76</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K5" s="2" t="n">
         <v>91894</v>
@@ -817,7 +817,7 @@
         <v>-1945.439999999991</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K8" s="2" t="n">
         <v>100833.76</v>
@@ -863,7 +863,7 @@
         <v>-972.7200000000039</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K9" s="2" t="n">
         <v>99861.03999999999</v>
@@ -909,7 +909,7 @@
         <v>-1945.440000000008</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K10" s="2" t="n">
         <v>97915.59999999999</v>
@@ -1047,7 +1047,7 @@
         <v>-2269.679999999993</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K13" s="2" t="n">
         <v>101111.68</v>
@@ -1093,7 +1093,7 @@
         <v>-2223.360000000002</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K14" s="2" t="n">
         <v>98888.31999999999</v>
@@ -1185,7 +1185,7 @@
         <v>-5465.759999999998</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K16" s="2" t="n">
         <v>99444.15999999999</v>
@@ -1231,7 +1231,7 @@
         <v>-416.8799999999993</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K17" s="2" t="n">
         <v>99027.28</v>
@@ -1277,7 +1277,7 @@
         <v>-5280.480000000002</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K18" s="2" t="n">
         <v>93746.79999999999</v>
@@ -1323,7 +1323,7 @@
         <v>-1667.519999999997</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K19" s="2" t="n">
         <v>92079.28</v>
@@ -1415,7 +1415,7 @@
         <v>-3057.120000000001</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K21" s="2" t="n">
         <v>95136.39999999999</v>
@@ -1645,7 +1645,7 @@
         <v>-3751.920000000011</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K26" s="2" t="n">
         <v>102871.84</v>
